--- a/data-raw/correspondencia_mun_terr_desenvol.xlsx
+++ b/data-raw/correspondencia_mun_terr_desenvol.xlsx
@@ -33299,8 +33299,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -33587,7 +33587,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27BBA623-37E5-4AD4-BD04-0304867D10B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3096B794-6F51-41B2-A137-1BAE359AB1B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
